--- a/tame_output/MOZAIC/data/universe_last2023-07-31.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-31.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.9484402047764</v>
+        <v>568.6121016788368</v>
       </c>
       <c r="E2" t="n">
-        <v>12068.12691625043</v>
+        <v>11743.32574929432</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6056982699090272</v>
+        <v>0.6099624406191504</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4959502326995601</v>
+        <v>0.4959321551366896</v>
       </c>
       <c r="H2" t="n">
-        <v>1.221288407532517</v>
+        <v>1.229931220029545</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.7326304553236</v>
+        <v>225.0847358604498</v>
       </c>
       <c r="E3" t="n">
-        <v>5106.766790300402</v>
+        <v>4587.950631032174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2527475585567762</v>
+        <v>0.2520007667737558</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5946772661073869</v>
+        <v>0.594678797075414</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4250163457755841</v>
+        <v>0.423759461432082</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906368559842504</v>
+        <v>0.8906601608447614</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06793273939654</v>
+        <v>1.068002361952458</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.31030318786758</v>
+        <v>37.49142011682321</v>
       </c>
       <c r="E4" t="n">
-        <v>1086.423913796179</v>
+        <v>1344.139259209271</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.325902484680335</v>
+        <v>0.7708391059983832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.558362901225738</v>
+        <v>1.102556289953439</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5836750327876411</v>
+        <v>0.6991380966417012</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J4" t="n">
         <v>273</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7361339247736141</v>
+        <v>0.4735875402852985</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8287724187363785</v>
+        <v>1.052879745700732</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.0402824602188</v>
+        <v>37.15501246478819</v>
       </c>
       <c r="E5" t="n">
-        <v>1325.161514259285</v>
+        <v>1081.315694630769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7426153375464388</v>
+        <v>-0.3292452956162151</v>
       </c>
       <c r="G5" t="n">
-        <v>1.102541873561295</v>
+        <v>0.5583735152071654</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6735484205672243</v>
+        <v>-0.5896506310727504</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J5" t="n">
         <v>273</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736715888122658</v>
+        <v>0.7361960284249801</v>
       </c>
       <c r="N5" t="n">
-        <v>1.05301444892798</v>
+        <v>0.8288883066271634</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.00924798792102</v>
+        <v>10.88318593959072</v>
       </c>
       <c r="E6" t="n">
-        <v>383.8189299675675</v>
+        <v>342.5387078303801</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4752367592701338</v>
+        <v>-0.4817659564470412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8116450659670924</v>
+        <v>0.8116444938230035</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5855228833355612</v>
+        <v>-0.5935677012700842</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6664881936108292</v>
+        <v>0.6666184487724361</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090738179363353</v>
+        <v>1.090990345802144</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.9277348663201</v>
+        <v>10.85818014503612</v>
       </c>
       <c r="E7" t="n">
-        <v>197.1944416732479</v>
+        <v>186.525565519177</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2968363198214825</v>
+        <v>-0.3013582897619396</v>
       </c>
       <c r="G7" t="n">
-        <v>0.710760791567327</v>
+        <v>0.7108914599759116</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4176318155745717</v>
+        <v>-0.4239160360319296</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7505942491116666</v>
+        <v>0.7504349171545419</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075698583183596</v>
+        <v>1.075707167497249</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.744572338237484</v>
+        <v>9.647596296867539</v>
       </c>
       <c r="E8" t="n">
-        <v>449.8495525100218</v>
+        <v>385.0113951878013</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3330514893020367</v>
+        <v>-0.3378671356542793</v>
       </c>
       <c r="G8" t="n">
-        <v>1.166032551478349</v>
+        <v>1.166104122329356</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2856279517066472</v>
+        <v>-0.2897401091245362</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372727850187963</v>
+        <v>0.737243074476915</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733407930815107</v>
+        <v>1.73350765704907</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.999143435617174</v>
+        <v>6.998619962292807</v>
       </c>
       <c r="E9" t="n">
-        <v>276.0976617165306</v>
+        <v>259.831748303825</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3268681959242794</v>
+        <v>0.326187235018405</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4819532092880184</v>
+        <v>0.4819782235835401</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6782156226475936</v>
+        <v>0.6767675779896883</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6736486722524992</v>
+        <v>0.6733790757146892</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6546365302773908</v>
+        <v>0.6544323600510195</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.832950386695169</v>
+        <v>6.76779462328395</v>
       </c>
       <c r="E10" t="n">
-        <v>654.0840686779521</v>
+        <v>570.9823478827169</v>
       </c>
       <c r="F10" t="n">
-        <v>1.01292694265326</v>
+        <v>0.9958403333178831</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8177577362073776</v>
+        <v>0.8179476872988879</v>
       </c>
       <c r="H10" t="n">
-        <v>1.238663846032255</v>
+        <v>1.217486581087418</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6637946920717175</v>
+        <v>0.6636139081109997</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094511523344472</v>
+        <v>1.094507496189999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.522812340621185</v>
+        <v>6.408111495429364</v>
       </c>
       <c r="E11" t="n">
-        <v>114.4949819508996</v>
+        <v>229.5166199823458</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2879576069642811</v>
+        <v>-0.3030489541155033</v>
       </c>
       <c r="G11" t="n">
-        <v>0.655009040874581</v>
+        <v>0.9539699140165238</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4396238662290743</v>
+        <v>-0.3176713957776389</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J11" t="n">
         <v>273</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7888262176151657</v>
+        <v>0.7131442541475747</v>
       </c>
       <c r="N11" t="n">
-        <v>1.041814823645493</v>
+        <v>1.371796839071726</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.472172673405749</v>
+        <v>6.386160460220102</v>
       </c>
       <c r="E12" t="n">
-        <v>248.6065305530338</v>
+        <v>110.3732770345459</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.296549704333237</v>
+        <v>-0.2935139440740414</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9538854721821507</v>
+        <v>0.655149341450959</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3108860685914807</v>
+        <v>-0.4480107442739638</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J12" t="n">
         <v>273</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7131645012662355</v>
+        <v>0.7886698932218743</v>
       </c>
       <c r="N12" t="n">
-        <v>1.371664356988</v>
+        <v>1.041869448904954</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.874431884088143</v>
+        <v>4.863773712754963</v>
       </c>
       <c r="E13" t="n">
-        <v>387.259335035757</v>
+        <v>365.50767077823</v>
       </c>
       <c r="F13" t="n">
-        <v>1.825685072491421</v>
+        <v>1.821154284640474</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8579405080804647</v>
+        <v>0.8579694953849517</v>
       </c>
       <c r="H13" t="n">
-        <v>2.127985629884949</v>
+        <v>2.122632907622622</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6018743618695281</v>
+        <v>0.6017909792422727</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041177847648596</v>
+        <v>1.041106726877591</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.491532919499637</v>
+        <v>4.445924292140434</v>
       </c>
       <c r="E14" t="n">
-        <v>106.3794095683146</v>
+        <v>107.1570554957591</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4114094567054554</v>
+        <v>-0.4192837420508302</v>
       </c>
       <c r="G14" t="n">
-        <v>0.845728361586661</v>
+        <v>0.8459748427068591</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4864557881606512</v>
+        <v>-0.4956219982963693</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602477335833553</v>
+        <v>0.7600615592992521</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296426592288589</v>
+        <v>1.296534115434584</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.203909018960947</v>
+        <v>4.217119765015206</v>
       </c>
       <c r="E15" t="n">
-        <v>131.3581232400579</v>
+        <v>129.7365812708522</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5423164278285306</v>
+        <v>0.5449967693732762</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9558547234462217</v>
+        <v>0.9558224622481515</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5673628162585969</v>
+        <v>0.5701861913680196</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5139294597213645</v>
+        <v>0.5138525381937779</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9905064444045107</v>
+        <v>0.9903608652951066</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.111591549532892</v>
+        <v>4.044605064746865</v>
       </c>
       <c r="E16" t="n">
-        <v>219.5129968069474</v>
+        <v>214.6424451843542</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04113342136297249</v>
+        <v>-0.05491499077587925</v>
       </c>
       <c r="G16" t="n">
-        <v>0.791167735922529</v>
+        <v>0.7911377007409407</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.05199077198845766</v>
+        <v>-0.06941268343608017</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.712878970002415</v>
+        <v>0.7130683217205733</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137224671946596</v>
+        <v>1.137525015617767</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.798142261401609</v>
+        <v>3.754628565582955</v>
       </c>
       <c r="E17" t="n">
-        <v>149.0135160415306</v>
+        <v>145.0325327593255</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07024304242768553</v>
+        <v>-0.08360948373381227</v>
       </c>
       <c r="G17" t="n">
-        <v>0.752650372350179</v>
+        <v>0.7522445766365219</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.093327586098641</v>
+        <v>-0.1111466753374969</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7201298787890001</v>
+        <v>0.7208253764593412</v>
       </c>
       <c r="N17" t="n">
-        <v>1.092863730420649</v>
+        <v>1.093369273452467</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.100092374981651</v>
+        <v>3.07014578393477</v>
       </c>
       <c r="E18" t="n">
-        <v>66.01890933684844</v>
+        <v>63.94268874061191</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4672190440769819</v>
+        <v>-0.4724706889555613</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7419000790981117</v>
+        <v>0.7420324199247339</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6297600677505725</v>
+        <v>-0.6367251298851405</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644879547219776</v>
+        <v>0.7643975053869401</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143610057385284</v>
+        <v>1.143720415850765</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.94852281247402</v>
+        <v>2.938388316640782</v>
       </c>
       <c r="E19" t="n">
-        <v>63.46120162035282</v>
+        <v>61.41114702863985</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1031702436237429</v>
+        <v>0.09859210004786267</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4790611751869813</v>
+        <v>0.479042025665561</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2153592254339434</v>
+        <v>0.2058109618062902</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173157841701938</v>
+        <v>0.71745456573835</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6928883583222664</v>
+        <v>0.6930199724588861</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.649990253713697</v>
+        <v>2.631284535978882</v>
       </c>
       <c r="E20" t="n">
-        <v>148.4700703932762</v>
+        <v>136.7400266283456</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2975690358572612</v>
+        <v>-0.3021047165064223</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7744112067190223</v>
+        <v>0.7745373263613051</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3842519752754914</v>
+        <v>-0.3900453938426422</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321838394773049</v>
+        <v>0.7320419493897206</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143282799936247</v>
+        <v>1.143289073700729</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-31.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-31.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.6121016788368</v>
+        <v>568.5022745094185</v>
       </c>
       <c r="E2" t="n">
-        <v>11743.32574929432</v>
+        <v>11829.01690041965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6099624406191504</v>
+        <v>0.6083904406402696</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4959321551366896</v>
+        <v>0.4959376050146327</v>
       </c>
       <c r="H2" t="n">
-        <v>1.229931220029545</v>
+        <v>1.226747950727227</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.0847358604498</v>
+        <v>223.1439125812398</v>
       </c>
       <c r="E3" t="n">
-        <v>4587.950631032174</v>
+        <v>4464.207155900759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2520007667737558</v>
+        <v>0.2482595023805478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.594678797075414</v>
+        <v>0.59469311005367</v>
       </c>
       <c r="H3" t="n">
-        <v>0.423759461432082</v>
+        <v>0.4174581783167841</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906601608447614</v>
+        <v>0.8906664205726319</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068002361952458</v>
+        <v>1.068023836698329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.49142011682321</v>
+        <v>37.17973212750168</v>
       </c>
       <c r="E4" t="n">
-        <v>1344.139259209271</v>
+        <v>1095.503994609722</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7708391059983832</v>
+        <v>-0.3288740790922058</v>
       </c>
       <c r="G4" t="n">
-        <v>1.102556289953439</v>
+        <v>0.5583707294880966</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6991380966417012</v>
+        <v>-0.5889887519600304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J4" t="n">
         <v>273</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735875402852985</v>
+        <v>0.736196037587779</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052879745700732</v>
+        <v>0.8288750729882756</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.15501246478819</v>
+        <v>36.84568377123526</v>
       </c>
       <c r="E5" t="n">
-        <v>1081.315694630769</v>
+        <v>1489.973126963677</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3292452956162151</v>
+        <v>0.726066666296596</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5583735152071654</v>
+        <v>1.1026146988667</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5896506310727504</v>
+        <v>0.6584953629249353</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J5" t="n">
         <v>273</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7361960284249801</v>
+        <v>0.4736914930624683</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8288883066271634</v>
+        <v>1.053155069705554</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.88318593959072</v>
+        <v>10.91347760248462</v>
       </c>
       <c r="E6" t="n">
-        <v>342.5387078303801</v>
+        <v>350.3538125596057</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4817659564470412</v>
+        <v>-0.4806940798880107</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8116444938230035</v>
+        <v>0.811634818971871</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5935677012700842</v>
+        <v>-0.5922541377622567</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666184487724361</v>
+        <v>0.6666141754111324</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090990345802144</v>
+        <v>1.090958358699042</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.85818014503612</v>
+        <v>10.77080513491744</v>
       </c>
       <c r="E7" t="n">
-        <v>186.525565519177</v>
+        <v>195.9003528778362</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3013582897619396</v>
+        <v>-0.309479259194014</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7108914599759116</v>
+        <v>0.7112321554082169</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4239160360319296</v>
+        <v>-0.4351311408528571</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7504349171545419</v>
+        <v>0.750215612408349</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075707167497249</v>
+        <v>1.075896366072789</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.647596296867539</v>
+        <v>9.629762142312172</v>
       </c>
       <c r="E8" t="n">
-        <v>385.0113951878013</v>
+        <v>377.3335786694087</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3378671356542793</v>
+        <v>-0.3423045272456098</v>
       </c>
       <c r="G8" t="n">
-        <v>1.166104122329356</v>
+        <v>1.166199026824516</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2897401091245362</v>
+        <v>-0.2935215339509267</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.737243074476915</v>
+        <v>0.7372348850756639</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73350765704907</v>
+        <v>1.733610431681129</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.998619962292807</v>
+        <v>7.006324663964727</v>
       </c>
       <c r="E9" t="n">
-        <v>259.831748303825</v>
+        <v>256.5631836695155</v>
       </c>
       <c r="F9" t="n">
-        <v>0.326187235018405</v>
+        <v>0.3275492449284951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4819782235835401</v>
+        <v>0.4819285785769029</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6767675779896883</v>
+        <v>0.6796634594605746</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6733790757146892</v>
+        <v>0.6735268226539899</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6544323600510195</v>
+        <v>0.6545013344279024</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.76779462328395</v>
+        <v>6.775048414859764</v>
       </c>
       <c r="E10" t="n">
-        <v>570.9823478827169</v>
+        <v>536.1622700694592</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9958403333178831</v>
+        <v>0.9938155469357977</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8179476872988879</v>
+        <v>0.8179744328641496</v>
       </c>
       <c r="H10" t="n">
-        <v>1.217486581087418</v>
+        <v>1.214971406203905</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6636139081109997</v>
+        <v>0.6636445828374238</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094507496189999</v>
+        <v>1.094581850178088</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.408111495429364</v>
+        <v>6.409597723214052</v>
       </c>
       <c r="E11" t="n">
-        <v>229.5166199823458</v>
+        <v>227.7156145886306</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3030489541155033</v>
+        <v>-0.3045362215485613</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9539699140165238</v>
+        <v>0.9539984866414767</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3176713957776389</v>
+        <v>-0.3192208644068944</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7131442541475747</v>
+        <v>0.7131540625035807</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371796839071726</v>
+        <v>1.37184171857781</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.386160460220102</v>
+        <v>6.322262916426127</v>
       </c>
       <c r="E12" t="n">
-        <v>110.3732770345459</v>
+        <v>108.7713250985645</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2935139440740414</v>
+        <v>-0.292958804336018</v>
       </c>
       <c r="G12" t="n">
-        <v>0.655149341450959</v>
+        <v>0.6551322793090393</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4480107442739638</v>
+        <v>-0.4471750417259219</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7886698932218743</v>
+        <v>0.78871855838862</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041869448904954</v>
+        <v>1.041895153071182</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.863773712754963</v>
+        <v>4.859289188918005</v>
       </c>
       <c r="E13" t="n">
-        <v>365.50767077823</v>
+        <v>358.6278158740438</v>
       </c>
       <c r="F13" t="n">
-        <v>1.821154284640474</v>
+        <v>1.813607046337035</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8579694953849517</v>
+        <v>0.8580226074838709</v>
       </c>
       <c r="H13" t="n">
-        <v>2.122632907622622</v>
+        <v>2.113705432139359</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6017909792422727</v>
+        <v>0.6018038625745908</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041106726877591</v>
+        <v>1.041182023986425</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.445924292140434</v>
+        <v>4.438335046746393</v>
       </c>
       <c r="E14" t="n">
-        <v>107.1570554957591</v>
+        <v>109.0712145849803</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4192837420508302</v>
+        <v>-0.419888347661312</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8459748427068591</v>
+        <v>0.846000138536332</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4956219982963693</v>
+        <v>-0.4963218426745915</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600615592992521</v>
+        <v>0.7600860475926559</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296534115434584</v>
+        <v>1.296600409125957</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.217119765015206</v>
+        <v>4.091327552253492</v>
       </c>
       <c r="E15" t="n">
-        <v>129.7365812708522</v>
+        <v>140.1942387698441</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5449967693732762</v>
+        <v>0.4836476412780704</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9558224622481515</v>
+        <v>0.9571336349783778</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5701861913680196</v>
+        <v>0.5053083745082224</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5138525381937779</v>
+        <v>0.5134378938064472</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9903608652951066</v>
+        <v>0.9909082768992833</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.044605064746865</v>
+        <v>4.047560084026337</v>
       </c>
       <c r="E16" t="n">
-        <v>214.6424451843542</v>
+        <v>211.6062939377035</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.05491499077587925</v>
+        <v>-0.05625683783177349</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7911377007409407</v>
+        <v>0.7911452832583864</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06941268343608017</v>
+        <v>-0.0711080998929499</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7130683217205733</v>
+        <v>0.7130741839775134</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137525015617767</v>
+        <v>1.137532769370227</v>
       </c>
     </row>
     <row r="17">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.754628565582955</v>
+        <v>3.766661844377261</v>
       </c>
       <c r="E17" t="n">
-        <v>145.0325327593255</v>
+        <v>145.5202988782942</v>
       </c>
       <c r="F17" t="n">
         <v>-0.08360948373381227</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7208253764593412</v>
+        <v>0.7207777291541035</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093369273452467</v>
+        <v>1.093284986325174</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.07014578393477</v>
+        <v>3.07418628071749</v>
       </c>
       <c r="E18" t="n">
-        <v>63.94268874061191</v>
+        <v>64.06882637931136</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4724706889555613</v>
+        <v>-0.4725501584051928</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7420324199247339</v>
+        <v>0.7420351585821143</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6367251298851405</v>
+        <v>-0.6368298765090117</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7643975053869401</v>
+        <v>0.7644237054768839</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143720415850765</v>
+        <v>1.143751269881482</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.938388316640782</v>
+        <v>2.952601537340044</v>
       </c>
       <c r="E19" t="n">
-        <v>61.41114702863985</v>
+        <v>62.01934552459128</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09859210004786267</v>
+        <v>0.1068362105467371</v>
       </c>
       <c r="G19" t="n">
-        <v>0.479042025665561</v>
+        <v>0.4790957753487787</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2058109618062902</v>
+        <v>0.2229955178981927</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.71745456573835</v>
+        <v>0.7172645946947979</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6930199724588861</v>
+        <v>0.6929065948031761</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.631284535978882</v>
+        <v>2.632694300350604</v>
       </c>
       <c r="E20" t="n">
-        <v>136.7400266283456</v>
+        <v>133.2164131213538</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3021047165064223</v>
+        <v>-0.3026082235651286</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7745373263613051</v>
+        <v>0.7745537290327277</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3900453938426422</v>
+        <v>-0.3906871947321582</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320419493897206</v>
+        <v>0.7320690601064819</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143289073700729</v>
+        <v>1.143343063081956</v>
       </c>
     </row>
   </sheetData>
